--- a/outputs/tables/shap_displacement_11a_11b.xlsx
+++ b/outputs/tables/shap_displacement_11a_11b.xlsx
@@ -456,19 +456,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.6</v>
+        <v>19.05</v>
       </c>
       <c r="C2" t="n">
-        <v>2.65</v>
+        <v>3.06</v>
       </c>
       <c r="D2" t="n">
-        <v>20.62</v>
+        <v>26.9</v>
       </c>
       <c r="E2" t="n">
-        <v>15.18</v>
+        <v>15.47</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.44</v>
+        <v>-11.43</v>
       </c>
     </row>
     <row r="3">
@@ -478,19 +478,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.41</v>
+        <v>40.8</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.44</v>
+        <v>0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>1.16</v>
+        <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.28</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.23</v>
+        <v>30.18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.71</v>
+        <v>0.92</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>6.06</v>
+        <v>7.64</v>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="5">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.34</v>
+        <v>28.45</v>
       </c>
       <c r="C5" t="n">
-        <v>1.17</v>
+        <v>0.14</v>
       </c>
       <c r="D5" t="n">
-        <v>4.36</v>
+        <v>2.28</v>
       </c>
       <c r="E5" t="n">
-        <v>10.88</v>
+        <v>1.08</v>
       </c>
       <c r="F5" t="n">
-        <v>6.52</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="6">
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.85</v>
+        <v>31.32</v>
       </c>
       <c r="C6" t="n">
-        <v>0.64</v>
+        <v>0.1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.83</v>
+        <v>1.72</v>
       </c>
       <c r="E6" t="n">
-        <v>3.67</v>
+        <v>0.96</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.16</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="7">
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.48</v>
+        <v>30.88</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="D7" t="n">
-        <v>23.27</v>
+        <v>20.78</v>
       </c>
       <c r="E7" t="n">
-        <v>19.35</v>
+        <v>11.52</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.93</v>
+        <v>-9.27</v>
       </c>
     </row>
     <row r="8">
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.32</v>
+        <v>30.11</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="D8" t="n">
-        <v>9.710000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="E8" t="n">
-        <v>9.380000000000001</v>
+        <v>6.12</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.33</v>
+        <v>-4.08</v>
       </c>
     </row>
   </sheetData>
@@ -647,12 +647,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Credit-to-GDP gap</t>
+          <t>NFA change (%GDP)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>credit_gap</t>
+          <t>nfa_gdp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.78</v>
+        <v>9.25</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.86</v>
+        <v>7.47</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -693,12 +693,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Private credit (%GDP)</t>
+          <t>Credit-to-GDP gap</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FS.AST.PRVT.GD.ZS</t>
+          <t>credit_gap</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -707,21 +707,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.85</v>
+        <v>6.77</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NFA growth</t>
+          <t>Private credit (%GDP)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nfa_g</t>
+          <t>FS.AST.PRVT.GD.ZS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.83</v>
+        <v>6.62</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
         <v>18</v>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.38</v>
+        <v>0.23</v>
       </c>
       <c r="E8" t="n">
         <v>25</v>

--- a/outputs/tables/shap_displacement_11a_11b.xlsx
+++ b/outputs/tables/shap_displacement_11a_11b.xlsx
@@ -456,19 +456,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.6</v>
+        <v>19.1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="D2" t="n">
-        <v>20.62</v>
+        <v>26.9</v>
       </c>
       <c r="E2" t="n">
-        <v>15.18</v>
+        <v>15.53</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.44</v>
+        <v>-11.36</v>
       </c>
     </row>
     <row r="3">
@@ -478,19 +478,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.41</v>
+        <v>40.29</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.44</v>
+        <v>0.83</v>
       </c>
       <c r="E3" t="n">
-        <v>1.16</v>
+        <v>0.16</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.28</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.23</v>
+        <v>31.27</v>
       </c>
       <c r="C4" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>11.89</v>
       </c>
       <c r="E4" t="n">
-        <v>6.06</v>
+        <v>7.45</v>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="5">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.34</v>
+        <v>28.22</v>
       </c>
       <c r="C5" t="n">
-        <v>1.17</v>
+        <v>0.59</v>
       </c>
       <c r="D5" t="n">
-        <v>4.36</v>
+        <v>6.02</v>
       </c>
       <c r="E5" t="n">
-        <v>10.88</v>
+        <v>3.53</v>
       </c>
       <c r="F5" t="n">
-        <v>6.52</v>
+        <v>-2.48</v>
       </c>
     </row>
     <row r="6">
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.85</v>
+        <v>28.81</v>
       </c>
       <c r="C6" t="n">
-        <v>0.64</v>
+        <v>0.06</v>
       </c>
       <c r="D6" t="n">
-        <v>3.83</v>
+        <v>1.11</v>
       </c>
       <c r="E6" t="n">
-        <v>3.67</v>
+        <v>0.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.16</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="7">
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.48</v>
+        <v>30.92</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>2.16</v>
       </c>
       <c r="D7" t="n">
-        <v>23.27</v>
+        <v>19.82</v>
       </c>
       <c r="E7" t="n">
-        <v>19.35</v>
+        <v>11.54</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.93</v>
+        <v>-8.279999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.32</v>
+        <v>29.77</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5</v>
+        <v>1.09</v>
       </c>
       <c r="D8" t="n">
-        <v>9.710000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="n">
-        <v>9.380000000000001</v>
+        <v>6.48</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.33</v>
+        <v>-4.61</v>
       </c>
     </row>
   </sheetData>
@@ -647,12 +647,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Credit-to-GDP gap</t>
+          <t>NFA change (%GDP)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>credit_gap</t>
+          <t>nfa_gdp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.78</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.86</v>
+        <v>6.9</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -693,12 +693,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Private credit (%GDP)</t>
+          <t>Credit-to-GDP gap</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FS.AST.PRVT.GD.ZS</t>
+          <t>credit_gap</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -707,21 +707,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.85</v>
+        <v>6.57</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NFA growth</t>
+          <t>Private credit (%GDP)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nfa_g</t>
+          <t>FS.AST.PRVT.GD.ZS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.83</v>
+        <v>6.43</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.64</v>
+        <v>0.44</v>
       </c>
       <c r="E6" t="n">
         <v>18</v>
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/shap_displacement_11a_11b.xlsx
+++ b/outputs/tables/shap_displacement_11a_11b.xlsx
@@ -456,19 +456,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.6</v>
+        <v>18.97</v>
       </c>
       <c r="C2" t="n">
-        <v>2.65</v>
+        <v>3.03</v>
       </c>
       <c r="D2" t="n">
-        <v>20.62</v>
+        <v>26.89</v>
       </c>
       <c r="E2" t="n">
-        <v>15.18</v>
+        <v>15.41</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.44</v>
+        <v>-11.48</v>
       </c>
     </row>
     <row r="3">
@@ -478,19 +478,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.41</v>
+        <v>44.5</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.44</v>
+        <v>0.23</v>
       </c>
       <c r="E3" t="n">
-        <v>1.16</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.28</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.23</v>
+        <v>30.74</v>
       </c>
       <c r="C4" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>12.02</v>
       </c>
       <c r="E4" t="n">
-        <v>6.06</v>
+        <v>5.81</v>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>-6.21</v>
       </c>
     </row>
     <row r="5">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.34</v>
+        <v>28.22</v>
       </c>
       <c r="C5" t="n">
-        <v>1.17</v>
+        <v>0.44</v>
       </c>
       <c r="D5" t="n">
-        <v>4.36</v>
+        <v>2.15</v>
       </c>
       <c r="E5" t="n">
-        <v>10.88</v>
+        <v>3.22</v>
       </c>
       <c r="F5" t="n">
-        <v>6.52</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="6">
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.85</v>
+        <v>29.96</v>
       </c>
       <c r="C6" t="n">
-        <v>0.64</v>
+        <v>0.08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.83</v>
+        <v>0.96</v>
       </c>
       <c r="E6" t="n">
-        <v>3.67</v>
+        <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="7">
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.48</v>
+        <v>32.6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>2.68</v>
       </c>
       <c r="D7" t="n">
-        <v>23.27</v>
+        <v>28.1</v>
       </c>
       <c r="E7" t="n">
-        <v>19.35</v>
+        <v>13.6</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.93</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="8">
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.32</v>
+        <v>30.83</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="D8" t="n">
-        <v>9.710000000000001</v>
+        <v>11.72</v>
       </c>
       <c r="E8" t="n">
-        <v>9.380000000000001</v>
+        <v>6.51</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.33</v>
+        <v>-5.22</v>
       </c>
     </row>
   </sheetData>
@@ -647,12 +647,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Credit-to-GDP gap</t>
+          <t>NFA change (%GDP)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>credit_gap</t>
+          <t>nfa_gdp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.78</v>
+        <v>9.75</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.86</v>
+        <v>7.36</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -693,12 +693,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Private credit (%GDP)</t>
+          <t>Credit-to-GDP gap</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FS.AST.PRVT.GD.ZS</t>
+          <t>credit_gap</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -707,21 +707,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.85</v>
+        <v>6.88</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NFA growth</t>
+          <t>Private credit (%GDP)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nfa_g</t>
+          <t>FS.AST.PRVT.GD.ZS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -730,21 +730,21 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.83</v>
+        <v>6.84</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Loans/deposits</t>
+          <t>Log off-bal. items</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>r_loans_dep</t>
+          <t>l_obsi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.64</v>
+        <v>0.51</v>
       </c>
       <c r="E6" t="n">
         <v>18</v>
@@ -762,12 +762,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Log off-bal. items</t>
+          <t>Loans/deposits</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>l_obsi</t>
+          <t>r_loans_dep</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/shap_displacement_11a_11b.xlsx
+++ b/outputs/tables/shap_displacement_11a_11b.xlsx
@@ -456,19 +456,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.6</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="D2" t="n">
-        <v>20.62</v>
+        <v>26.9</v>
       </c>
       <c r="E2" t="n">
-        <v>15.18</v>
+        <v>15.46</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.44</v>
+        <v>-11.43</v>
       </c>
     </row>
     <row r="3">
@@ -478,19 +478,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.41</v>
+        <v>45.65</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="D3" t="n">
-        <v>1.44</v>
+        <v>0.74</v>
       </c>
       <c r="E3" t="n">
-        <v>1.16</v>
+        <v>0.61</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.28</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.23</v>
+        <v>32.2</v>
       </c>
       <c r="C4" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>13.72</v>
       </c>
       <c r="E4" t="n">
-        <v>6.06</v>
+        <v>6.63</v>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>-7.09</v>
       </c>
     </row>
     <row r="5">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.34</v>
+        <v>22.26</v>
       </c>
       <c r="C5" t="n">
-        <v>1.17</v>
+        <v>0.87</v>
       </c>
       <c r="D5" t="n">
-        <v>4.36</v>
+        <v>4.74</v>
       </c>
       <c r="E5" t="n">
-        <v>10.88</v>
+        <v>3.75</v>
       </c>
       <c r="F5" t="n">
-        <v>6.52</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="6">
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.85</v>
+        <v>31.04</v>
       </c>
       <c r="C6" t="n">
-        <v>0.64</v>
+        <v>0.09</v>
       </c>
       <c r="D6" t="n">
-        <v>3.83</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
-        <v>3.67</v>
+        <v>0.77</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.16</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="7">
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.48</v>
+        <v>32.94</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>2.56</v>
       </c>
       <c r="D7" t="n">
-        <v>23.27</v>
+        <v>19.71</v>
       </c>
       <c r="E7" t="n">
-        <v>19.35</v>
+        <v>11.79</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.93</v>
+        <v>-7.92</v>
       </c>
     </row>
     <row r="8">
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.32</v>
+        <v>30.52</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="D8" t="n">
-        <v>9.710000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="n">
-        <v>9.380000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.33</v>
+        <v>-4.6</v>
       </c>
     </row>
   </sheetData>
@@ -647,12 +647,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Credit-to-GDP gap</t>
+          <t>NFA change (%GDP)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>credit_gap</t>
+          <t>nfa_gdp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.78</v>
+        <v>9.34</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -670,12 +670,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Credit growth</t>
+          <t>Credit-to-GDP gap</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>credit_g</t>
+          <t>credit_gap</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.86</v>
+        <v>8.08</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -693,12 +693,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Private credit (%GDP)</t>
+          <t>Credit growth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FS.AST.PRVT.GD.ZS</t>
+          <t>credit_g</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -707,21 +707,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.85</v>
+        <v>7.1</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NFA growth</t>
+          <t>Private credit (%GDP)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nfa_g</t>
+          <t>FS.AST.PRVT.GD.ZS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.83</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>8</v>
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.48</v>
+        <v>0.37</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/shap_displacement_11a_11b.xlsx
+++ b/outputs/tables/shap_displacement_11a_11b.xlsx
@@ -456,19 +456,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.6</v>
+        <v>19.13</v>
       </c>
       <c r="C2" t="n">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="D2" t="n">
-        <v>20.62</v>
+        <v>26.89</v>
       </c>
       <c r="E2" t="n">
-        <v>15.18</v>
+        <v>15.55</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.44</v>
+        <v>-11.34</v>
       </c>
     </row>
     <row r="3">
@@ -478,19 +478,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.41</v>
+        <v>40.61</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1.44</v>
+        <v>0.49</v>
       </c>
       <c r="E3" t="n">
-        <v>1.16</v>
+        <v>0.06</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.28</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.23</v>
+        <v>33.03</v>
       </c>
       <c r="C4" t="n">
-        <v>0.71</v>
+        <v>0.58</v>
       </c>
       <c r="D4" t="n">
-        <v>4.75</v>
+        <v>11.11</v>
       </c>
       <c r="E4" t="n">
-        <v>6.06</v>
+        <v>6.73</v>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="5">
@@ -522,19 +522,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.34</v>
+        <v>26.31</v>
       </c>
       <c r="C5" t="n">
-        <v>1.17</v>
+        <v>0.82</v>
       </c>
       <c r="D5" t="n">
-        <v>4.36</v>
+        <v>1.94</v>
       </c>
       <c r="E5" t="n">
-        <v>10.88</v>
+        <v>4.94</v>
       </c>
       <c r="F5" t="n">
-        <v>6.52</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="6">
@@ -544,19 +544,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.85</v>
+        <v>24.03</v>
       </c>
       <c r="C6" t="n">
-        <v>0.64</v>
+        <v>0.05</v>
       </c>
       <c r="D6" t="n">
-        <v>3.83</v>
+        <v>1.18</v>
       </c>
       <c r="E6" t="n">
-        <v>3.67</v>
+        <v>0.53</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.16</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="7">
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.48</v>
+        <v>32.72</v>
       </c>
       <c r="C7" t="n">
-        <v>3.8</v>
+        <v>2.54</v>
       </c>
       <c r="D7" t="n">
-        <v>23.27</v>
+        <v>20.8</v>
       </c>
       <c r="E7" t="n">
-        <v>19.35</v>
+        <v>12.01</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.93</v>
+        <v>-8.789999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.32</v>
+        <v>29.31</v>
       </c>
       <c r="C8" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="D8" t="n">
-        <v>9.710000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="E8" t="n">
-        <v>9.380000000000001</v>
+        <v>6.64</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.33</v>
+        <v>-3.77</v>
       </c>
     </row>
   </sheetData>
@@ -647,12 +647,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Credit-to-GDP gap</t>
+          <t>NFA change (%GDP)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>credit_gap</t>
+          <t>nfa_gdp</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.78</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>4</v>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.86</v>
+        <v>6.94</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -693,12 +693,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Private credit (%GDP)</t>
+          <t>Credit-to-GDP gap</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FS.AST.PRVT.GD.ZS</t>
+          <t>credit_gap</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -707,21 +707,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.85</v>
+        <v>6.82</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NFA growth</t>
+          <t>Private credit (%GDP)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nfa_g</t>
+          <t>FS.AST.PRVT.GD.ZS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4.83</v>
+        <v>6.07</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -753,10 +753,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -776,10 +776,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -799,10 +799,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.38</v>
+        <v>0.27</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
